--- a/입력레이아웃.xlsx
+++ b/입력레이아웃.xlsx
@@ -887,7 +887,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="17">
-        <v>46620</v>
+        <v>46258</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>12</v>
@@ -937,7 +937,7 @@
       </c>
       <c r="F7" s="22">
         <f>+D6-D5</f>
-        <v>25072</v>
+        <v>25434</v>
       </c>
     </row>
     <row r="8" spans="1:6">
